--- a/results/Int Task Remove ACC -0.5/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_5_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6994202154205105</v>
+        <v>0.7038065521403543</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7091753942347152</v>
+        <v>0.7022276269870462</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7091753942347152</v>
+        <v>0.7061580031801962</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7056660411027753</v>
+        <v>0.7097377632857249</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6992089944997434</v>
+        <v>0.7157033798539578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6973136813341358</v>
+        <v>0.7168965741066207</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6979106331555484</v>
+        <v>0.7115617827400408</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6972438064031684</v>
+        <v>0.7184047375912586</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6986125747209525</v>
+        <v>0.7178081404649272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6906118951251772</v>
+        <v>0.7137720651376235</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6912086695990491</v>
+        <v>0.7146142886075841</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6799435538248011</v>
+        <v>0.716755228116821</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6795574682290748</v>
+        <v>0.7137720651376235</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6696614754676921</v>
+        <v>0.7210007508894867</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6649239906176057</v>
+        <v>0.719491700667146</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6606775811072374</v>
+        <v>0.7265456990915904</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6681180198224893</v>
+        <v>0.7225800307378758</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6714172161189051</v>
+        <v>0.714403422381898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6700135103356373</v>
+        <v>0.7186501865873474</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6700135103356373</v>
+        <v>0.7215280051274722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6711714124277353</v>
+        <v>0.7241951347894513</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6063565614865696</v>
+        <v>0.7261603228860262</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.560806087135103</v>
+        <v>0.692365507605904</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.555436890345661</v>
+        <v>0.6934182426064697</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5628762649756697</v>
+        <v>0.6975594850253057</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5652626534809952</v>
+        <v>0.6975594850253057</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.564139688854381</v>
+        <v>0.6790651514565731</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5736843561379806</v>
+        <v>0.6790649741090325</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5965274287479654</v>
+        <v>0.6594469665235235</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6242851564010226</v>
+        <v>0.6511648363809326</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6287071399765121</v>
+        <v>0.6358287078138971</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5628040845266754</v>
+        <v>0.6358631132367594</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5395013270916458</v>
+        <v>0.6331963382698613</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5113938700886702</v>
+        <v>0.6494082089920169</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5111131289320167</v>
+        <v>0.6234411594556566</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5032172617326925</v>
+        <v>0.632109729889055</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5032172617326925</v>
+        <v>0.619089582853756</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.4906176057159822</v>
+        <v>0.6233711071771486</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.4803357047064135</v>
+        <v>0.6125995496081861</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5096372426997545</v>
+        <v>0.6055460832263632</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.510411364714153</v>
+        <v>0.6247075982425567</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5112535881841137</v>
+        <v>0.5977215097383308</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5049024180627761</v>
+        <v>0.5997221673430111</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5061654872464063</v>
+        <v>0.592316666093243</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5050774600852758</v>
+        <v>0.5890878767704162</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5045862073980172</v>
+        <v>0.6161798417563366</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5096414990407272</v>
+        <v>0.6396943521547549</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.509887302731897</v>
+        <v>0.6398358754920951</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4890748594609415</v>
+        <v>0.6317647889227307</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4903733981526771</v>
+        <v>0.6135540340713002</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4794924171512097</v>
+        <v>0.6110275410089585</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4723683664482572</v>
+        <v>0.6115187936962172</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4804052249423</v>
+        <v>0.6252756424148634</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4842659035520229</v>
+        <v>0.6151310084016623</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4844749963023038</v>
+        <v>0.6178330755291253</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4955285364607035</v>
+        <v>0.6181138166857788</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5528660603981879</v>
+        <v>0.6108860176716183</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5428641911551106</v>
+        <v>0.6033407665599153</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5437067693201524</v>
+        <v>0.6033407665599153</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.544491709534523</v>
+        <v>0.5670581199812863</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5493363122990874</v>
+        <v>0.5844280701430804</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5365967290729016</v>
+        <v>0.5844280701430804</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5371580340386681</v>
+        <v>0.5847439261127583</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5395790053143964</v>
+        <v>0.5477201441622688</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5395790053143964</v>
+        <v>0.547088432222913</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5407716675244376</v>
+        <v>0.5352277834075769</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5408410104127835</v>
+        <v>0.5207686384284455</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5408410104127835</v>
+        <v>0.5057143151033067</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5289798295548258</v>
+        <v>0.4950112136849875</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5215042760265496</v>
+        <v>0.4860971942555004</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.493005767696713</v>
+        <v>0.4673900436381359</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4921653177021576</v>
+        <v>0.434258508159583</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5049049009283435</v>
+        <v>0.4381894163953545</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5100313089348045</v>
+        <v>0.4404004081830993</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4847970594359</v>
+        <v>0.4661624439626109</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4535271410902546</v>
+        <v>0.453072244648804</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4425071196170144</v>
+        <v>0.4324727957740209</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4376637582852337</v>
+        <v>0.4459130791328273</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4376637582852337</v>
+        <v>0.4403684856258045</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4383289889097489</v>
+        <v>0.4403684856258045</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4746541988981043</v>
+        <v>0.43914106329782</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4783751276458923</v>
+        <v>0.4487226188698493</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4972612219316481</v>
+        <v>0.4807657724921905</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5015436329927433</v>
+        <v>0.4819234972367479</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5012277770230654</v>
+        <v>0.4827658980542492</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4989816704222964</v>
+        <v>0.5044562116508112</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5018591342673401</v>
+        <v>0.5062807631477486</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4982795515093517</v>
+        <v>0.5001402819045565</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4978936432611659</v>
+        <v>0.5011229646266142</v>
       </c>
     </row>
   </sheetData>
